--- a/public/Data.xlsx
+++ b/public/Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Website-Project\IKS\iks-digital-repository\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD43DCF6-A42B-47A9-9411-BE2689F95037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191D07A5-1D69-4051-A2EB-E508243C4AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1930" uniqueCount="1114">
   <si>
     <t>Voucher No</t>
   </si>
@@ -2698,6 +2698,753 @@
   </si>
   <si>
     <t>Flower, seed</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/79</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/80</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/81</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/82</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/83</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/84</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/85</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/86</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/87</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/88</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/89</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/90</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/91</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/92</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/93</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/94</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/95</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/96</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/97</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/98</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/99</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/100</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/101</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/102</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/103</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/104</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/105</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/106</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/107</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/108</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/109</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/110</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/111</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/112</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/113</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/114</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/115</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/116</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/117</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/118</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/119</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/120</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/121</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/122</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/123</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/124</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/125</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/126</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/127</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/128</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/129</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/130</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/131</t>
+  </si>
+  <si>
+    <t>IKS/Trident/M/132</t>
+  </si>
+  <si>
+    <t>Pandanus amaryllifolius</t>
+  </si>
+  <si>
+    <t>Desmodium gangeticum</t>
+  </si>
+  <si>
+    <t>Achyranthes aspera</t>
+  </si>
+  <si>
+    <t>Oxalis corniculata</t>
+  </si>
+  <si>
+    <t>Lindenbergia indica</t>
+  </si>
+  <si>
+    <t>Justicia prostrata</t>
+  </si>
+  <si>
+    <t>Solanum nigrum</t>
+  </si>
+  <si>
+    <t>Spilanthes paniculata</t>
+  </si>
+  <si>
+    <t>Pennisetum pedicellatum</t>
+  </si>
+  <si>
+    <t>Mirabilis jalapa</t>
+  </si>
+  <si>
+    <t>Vetiveria zizannioides</t>
+  </si>
+  <si>
+    <t>Tinospora cordifolia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tephrosia purpurea </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tectona grandis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strychnos nux-vomica </t>
+  </si>
+  <si>
+    <t>Streblus asper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acacia nilotica </t>
+  </si>
+  <si>
+    <t>Andrographis paniculata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annona reticulate </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annona squamosa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argemone mexicana </t>
+  </si>
+  <si>
+    <t>Argyreia nervosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aristolochia indica </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bauhinia variegate </t>
+  </si>
+  <si>
+    <t>Calotropis gigantea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capparis zeylanica </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chenopodium album </t>
+  </si>
+  <si>
+    <t>Clerodendrum viscosum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coccinea grandis </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cynodon dactylon </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delonix regia </t>
+  </si>
+  <si>
+    <t>Dioscrorea pentaphylla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gmelina arborea </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heliotropium indicum </t>
+  </si>
+  <si>
+    <t>Leucas cephalotes</t>
+  </si>
+  <si>
+    <t>Mallotus phillippensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marsilea minuta </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melia azedarach </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nelumbo nucifera </t>
+  </si>
+  <si>
+    <t>Nymphaea nouchali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocimum basilicum </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paederia foetida </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phoenix sylvestris </t>
+  </si>
+  <si>
+    <t>Clerodendrum thomsoniae</t>
+  </si>
+  <si>
+    <t>Dactyloctenium aegyptium</t>
+  </si>
+  <si>
+    <t>Carya aquatica</t>
+  </si>
+  <si>
+    <t>Oldenlandia corymbosa</t>
+  </si>
+  <si>
+    <t>Eragrostis tenella</t>
+  </si>
+  <si>
+    <t>Averrhoa carambola</t>
+  </si>
+  <si>
+    <t>Murraya paniculata</t>
+  </si>
+  <si>
+    <t>Hypericum carinatum</t>
+  </si>
+  <si>
+    <t>Phyllanthus niruri</t>
+  </si>
+  <si>
+    <t>Parthenium hysterophorus</t>
+  </si>
+  <si>
+    <t>Pandanaceae</t>
+  </si>
+  <si>
+    <t>Oxalidaceae</t>
+  </si>
+  <si>
+    <t>Orobanchaceae</t>
+  </si>
+  <si>
+    <t>Solanaceae</t>
+  </si>
+  <si>
+    <t>Nyctaginaceae</t>
+  </si>
+  <si>
+    <t>Poaceae</t>
+  </si>
+  <si>
+    <t>Menispermaceae</t>
+  </si>
+  <si>
+    <t>Verbenaceae</t>
+  </si>
+  <si>
+    <t>Loganiaceae</t>
+  </si>
+  <si>
+    <t>Mimosaceae</t>
+  </si>
+  <si>
+    <t>Papaveraceae</t>
+  </si>
+  <si>
+    <t>Aristolochiaceae</t>
+  </si>
+  <si>
+    <t>Caesalpiniaceae</t>
+  </si>
+  <si>
+    <t>Capparaceae</t>
+  </si>
+  <si>
+    <t>Chenopodiaceae</t>
+  </si>
+  <si>
+    <t>Dioscoreaceae</t>
+  </si>
+  <si>
+    <t>Boraginaceae</t>
+  </si>
+  <si>
+    <t>Marsiliaceae</t>
+  </si>
+  <si>
+    <t>Nymphaeaceae</t>
+  </si>
+  <si>
+    <t>Juglandaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypericaceae </t>
+  </si>
+  <si>
+    <t>It is used to treat headaches, fever, inflammation</t>
+  </si>
+  <si>
+    <t>It has antimicrobial, antioxidant, wound healing, antifungal properties</t>
+  </si>
+  <si>
+    <t>It is used in decoctions, infusions, or fresh juices to treat fevers, digestive disorders, urinary tract infections, and liver ailments.</t>
+  </si>
+  <si>
+    <t>It is used traditionally in chronic bronchitis, sore throat, toothache and is applied to skin issues, cuts and wounds</t>
+  </si>
+  <si>
+    <t>It is an ayurvedic medicinal herb known for its anti-inflammatory, antioxidant, and respiratory benefits</t>
+  </si>
+  <si>
+    <t>It is used to treat fever, inflammation, pain, and stomach ailments</t>
+  </si>
+  <si>
+    <t>It has antihelmintic, analgesic and anti-inflammatory properties</t>
+  </si>
+  <si>
+    <t>It has anesthetic, anti-inflammatory, and antimicrobial properties</t>
+  </si>
+  <si>
+    <t>It is used in traditional medicine to help cure wounds, eye problems, and parasitic infections</t>
+  </si>
+  <si>
+    <t>It has Diuretic, Purgative, Would healing properties</t>
+  </si>
+  <si>
+    <t>It is used to treat Burning sensation, Ulcers, Vomiting, Cough, Asthma, Gout, Lumbago</t>
+  </si>
+  <si>
+    <t>It is used to treat Chronic fever, Jaundice, Seminal weakness, Diabetes</t>
+  </si>
+  <si>
+    <t>It is used to treat Chronic fever, Anaemia, Gingivitis, Pimples, Elephantasis, Boils</t>
+  </si>
+  <si>
+    <t>It is usef for Arthiritis, Leukoderma, Leprosy, Dysentery, Piles, Eczema</t>
+  </si>
+  <si>
+    <t>It is used for Cholera, Asthma, Anaemia, Malarial Fever, Paralysis, Stomachache</t>
+  </si>
+  <si>
+    <t>It is used to treat Ulcers, Sinusitis, Elephantiasis, Sore heals, Boils, Haemorrholds, Syphllis</t>
+  </si>
+  <si>
+    <t>It is used to treat Diarrhoea, Dysentry, Diabetics</t>
+  </si>
+  <si>
+    <t>It is used to treat Dysentery, Fever, Tonsillitis, Hypertension, Snake bite</t>
+  </si>
+  <si>
+    <t>It is edible and used to treat Diarrhoea, Indigestion</t>
+  </si>
+  <si>
+    <t>It is used to treat Mental depression, Spinal disorder, Anaemia</t>
+  </si>
+  <si>
+    <t>It is used to treat Juandice, Leprosy, Conjunctivitis</t>
+  </si>
+  <si>
+    <t>It is used to treat Anorexia, Colie, Piles, Synovitis, Cerebral disorder, Cardiac problem</t>
+  </si>
+  <si>
+    <t>It is used for Ulcer, Inflammation, Colic, Cough, Leukoderma</t>
+  </si>
+  <si>
+    <t>It is used for Skin diseases, Cough, Leprosy, Diabetes</t>
+  </si>
+  <si>
+    <t>It is used to treat Scabies, Acne, Pimples</t>
+  </si>
+  <si>
+    <t>It is used to treat Skin troubles</t>
+  </si>
+  <si>
+    <t>It is used to treat Peptic ulcer, Helminthiasis, Eye disorders, Seminal weakness</t>
+  </si>
+  <si>
+    <t>It is used to treat Tumour, leprosy, Skin disease, Cough, Bronchitis</t>
+  </si>
+  <si>
+    <t>It is used to treat Vomiting, Uterine discharges, Leprosy, Jaundice, Cough</t>
+  </si>
+  <si>
+    <t>It is used to treat Conjunctivitis, Wounds, Leprosy, Skin disease</t>
+  </si>
+  <si>
+    <t>It is used to treat Diabetes, Reduces blood sugar level, Anti inflammation</t>
+  </si>
+  <si>
+    <t>It is used to treat Syphillis, Dysentery, Piles, Aphrodisic, Worm infestation</t>
+  </si>
+  <si>
+    <t>It is used as Galactogouge, Laxative, Antihelminthic compound</t>
+  </si>
+  <si>
+    <t>It is used to treat Rheumatism, Ulcer Would, Gonorrhoea</t>
+  </si>
+  <si>
+    <t>It is used to treat Inflammation, Liver ailment, Diabetes</t>
+  </si>
+  <si>
+    <t>It is used to treat Cough, Renal disorder, Ring worm, Herpes, Scabies, Wound ulcer</t>
+  </si>
+  <si>
+    <t>It is used to treat Diarrhoea, Cough Bronchitis, Leprosy</t>
+  </si>
+  <si>
+    <t>It is used to treat Ascariasis, Vaginal infection, Trichomoniases</t>
+  </si>
+  <si>
+    <t>It is used to treat Neuoasthenia, Spermatorrhoea, Metrorrhhoea, Liver diseases</t>
+  </si>
+  <si>
+    <t>It is used to treat Diarrhoea, Dermatopathy, Cardiac disorders</t>
+  </si>
+  <si>
+    <t>it is used to treat Cold, Cough, Fever, Ring worm, Cancer, Stress, Asthma, Diabetes</t>
+  </si>
+  <si>
+    <t>It is used to treat Rheumatism, Bacillary dysentery, Dysuria, Gastrititis, Dyspepsia</t>
+  </si>
+  <si>
+    <t>It is used to treat Burning sensation, Fever, Cardiac debility, Gastropathy</t>
+  </si>
+  <si>
+    <t>It is used to treat  to help manage diabetes and related metabolic disorders</t>
+  </si>
+  <si>
+    <t>Decoctions of seeds are used to relieve kidney pain and typhoid fever. Dried grains are eaten post-childbirth to ease bellyaches</t>
+  </si>
+  <si>
+    <t>It is used to treat digestive imbalances</t>
+  </si>
+  <si>
+    <t>It is used as a decoction, infusion, or juice to treat fevers, jaundice, liver diseases, digestive issues, and inflammation</t>
+  </si>
+  <si>
+    <t>It has antimicrobial, antioxidant, and therapeutic properties</t>
+  </si>
+  <si>
+    <t>It is used for treatment of diabetes and diabetic nephropathy, arthralgia, vomiting, lithangiuria, coughing, hangovers</t>
+  </si>
+  <si>
+    <t>It is used in traditional remedies to treat diarrhea, dysentery, stomach aches, and abdominal pain. Crushed leaves or leaf poultices are applied externally to relieve swelling from sprains, contusions, snakebites, and inflamed joints</t>
+  </si>
+  <si>
+    <t>It has  anti-depressant, wound-healing attributes</t>
+  </si>
+  <si>
+    <t>It is traditionally utilized for kidney stones, urinary tract infections, and liver ailments like hepatitis</t>
+  </si>
+  <si>
+    <t>It is used for treatment of skin rashes, rheumatic pain, inflammation, and wound healing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annapurna </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akrutichchhatra </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ambiliti </t>
+  </si>
+  <si>
+    <t>Pitapapada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nunununia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anasorisho </t>
+  </si>
+  <si>
+    <t>Biri Biri</t>
+  </si>
+  <si>
+    <t>Dinanath</t>
+  </si>
+  <si>
+    <t>Rangini</t>
+  </si>
+  <si>
+    <t>Bena</t>
+  </si>
+  <si>
+    <t>Guluchi lata</t>
+  </si>
+  <si>
+    <t>Soroponkha</t>
+  </si>
+  <si>
+    <t>Saguan</t>
+  </si>
+  <si>
+    <t>Kochila</t>
+  </si>
+  <si>
+    <t>Sahada</t>
+  </si>
+  <si>
+    <t>Babul</t>
+  </si>
+  <si>
+    <t>Bhui Nimba</t>
+  </si>
+  <si>
+    <t>Ramphal</t>
+  </si>
+  <si>
+    <t>Sitaphal</t>
+  </si>
+  <si>
+    <t>Odosamari</t>
+  </si>
+  <si>
+    <t>Mundanoi</t>
+  </si>
+  <si>
+    <t>Iswara mula</t>
+  </si>
+  <si>
+    <t>Kanchana</t>
+  </si>
+  <si>
+    <t>Arakha</t>
+  </si>
+  <si>
+    <t>Kantikapali</t>
+  </si>
+  <si>
+    <t>Bathua</t>
+  </si>
+  <si>
+    <t>Sweta bhaunarmala</t>
+  </si>
+  <si>
+    <t>Duba</t>
+  </si>
+  <si>
+    <t>Krushnachuda</t>
+  </si>
+  <si>
+    <t>Banaalu</t>
+  </si>
+  <si>
+    <t>Gambari</t>
+  </si>
+  <si>
+    <t>Hatisundha</t>
+  </si>
+  <si>
+    <t>Guma</t>
+  </si>
+  <si>
+    <t>Sinduri</t>
+  </si>
+  <si>
+    <t>Sunsunia</t>
+  </si>
+  <si>
+    <t>Maha nimba</t>
+  </si>
+  <si>
+    <t>Padma</t>
+  </si>
+  <si>
+    <t>Nali Kain</t>
+  </si>
+  <si>
+    <t>Kapur Kranti</t>
+  </si>
+  <si>
+    <t>Pasaruni</t>
+  </si>
+  <si>
+    <t>Khajuri</t>
+  </si>
+  <si>
+    <t>Brajamalli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kakuria </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pani hickory </t>
+  </si>
+  <si>
+    <t>Gharpodia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jhusa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karamanga </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kamini </t>
+  </si>
+  <si>
+    <t>Narakoli</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Gajar ghas </t>
+  </si>
+  <si>
+    <t>Climbing vine</t>
+  </si>
+  <si>
+    <t>Root, leaf</t>
+  </si>
+  <si>
+    <t>Leaf, root, flower</t>
+  </si>
+  <si>
+    <t>Leaf, root, seed</t>
+  </si>
+  <si>
+    <t>Root, Leaves</t>
+  </si>
+  <si>
+    <t>Bark, leaves and seeds</t>
+  </si>
+  <si>
+    <t>Root, bark, latex, leaves</t>
+  </si>
+  <si>
+    <t>Bark, Gum</t>
+  </si>
+  <si>
+    <t>Root, Seed</t>
+  </si>
+  <si>
+    <t>Root, stem, leaf</t>
+  </si>
+  <si>
+    <t>Root, bark</t>
+  </si>
+  <si>
+    <t>Root, Bark, Leaves</t>
+  </si>
+  <si>
+    <t>Stem, bark, seed</t>
+  </si>
+  <si>
+    <t>Stem, Leaves, Seed</t>
+  </si>
+  <si>
+    <t>Rhizome, Tuber</t>
+  </si>
+  <si>
+    <t>Root, fruit</t>
+  </si>
+  <si>
+    <t>Wood &amp; nut</t>
+  </si>
+  <si>
+    <t>Leaf, stem, flower</t>
   </si>
 </sst>
 </file>
@@ -2733,12 +3480,18 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2754,8 +3507,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3096,7 +3850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H242"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.59765625" bestFit="1" customWidth="1"/>
@@ -7985,6 +8739,1404 @@
         <v>97</v>
       </c>
     </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A189" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="B189" t="s">
+        <v>919</v>
+      </c>
+      <c r="C189" t="s">
+        <v>972</v>
+      </c>
+      <c r="D189" t="s">
+        <v>993</v>
+      </c>
+      <c r="E189" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F189" t="s">
+        <v>29</v>
+      </c>
+      <c r="G189" t="s">
+        <v>52</v>
+      </c>
+      <c r="H189" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>866</v>
+      </c>
+      <c r="B190" t="s">
+        <v>920</v>
+      </c>
+      <c r="C190" t="s">
+        <v>18</v>
+      </c>
+      <c r="D190" t="s">
+        <v>994</v>
+      </c>
+      <c r="E190" t="s">
+        <v>836</v>
+      </c>
+      <c r="F190" t="s">
+        <v>13</v>
+      </c>
+      <c r="G190" t="s">
+        <v>22</v>
+      </c>
+      <c r="H190" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>867</v>
+      </c>
+      <c r="B191" t="s">
+        <v>921</v>
+      </c>
+      <c r="C191" t="s">
+        <v>26</v>
+      </c>
+      <c r="D191" t="s">
+        <v>790</v>
+      </c>
+      <c r="E191" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F191" t="s">
+        <v>29</v>
+      </c>
+      <c r="G191" t="s">
+        <v>30</v>
+      </c>
+      <c r="H191" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>868</v>
+      </c>
+      <c r="B192" t="s">
+        <v>922</v>
+      </c>
+      <c r="C192" t="s">
+        <v>973</v>
+      </c>
+      <c r="D192" t="s">
+        <v>995</v>
+      </c>
+      <c r="E192" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F192" t="s">
+        <v>29</v>
+      </c>
+      <c r="G192" t="s">
+        <v>14</v>
+      </c>
+      <c r="H192" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>869</v>
+      </c>
+      <c r="B193" t="s">
+        <v>923</v>
+      </c>
+      <c r="C193" t="s">
+        <v>974</v>
+      </c>
+      <c r="D193" t="s">
+        <v>996</v>
+      </c>
+      <c r="F193" t="s">
+        <v>29</v>
+      </c>
+      <c r="G193" t="s">
+        <v>30</v>
+      </c>
+      <c r="H193" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>870</v>
+      </c>
+      <c r="B194" t="s">
+        <v>924</v>
+      </c>
+      <c r="C194" t="s">
+        <v>312</v>
+      </c>
+      <c r="D194" t="s">
+        <v>997</v>
+      </c>
+      <c r="E194" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F194" t="s">
+        <v>29</v>
+      </c>
+      <c r="G194" t="s">
+        <v>22</v>
+      </c>
+      <c r="H194" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>871</v>
+      </c>
+      <c r="B195" t="s">
+        <v>925</v>
+      </c>
+      <c r="C195" t="s">
+        <v>975</v>
+      </c>
+      <c r="D195" t="s">
+        <v>998</v>
+      </c>
+      <c r="E195" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F195" t="s">
+        <v>29</v>
+      </c>
+      <c r="G195" t="s">
+        <v>65</v>
+      </c>
+      <c r="H195" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>872</v>
+      </c>
+      <c r="B196" t="s">
+        <v>486</v>
+      </c>
+      <c r="C196" t="s">
+        <v>123</v>
+      </c>
+      <c r="D196" t="s">
+        <v>999</v>
+      </c>
+      <c r="E196" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F196" t="s">
+        <v>29</v>
+      </c>
+      <c r="G196" t="s">
+        <v>52</v>
+      </c>
+      <c r="H196" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>873</v>
+      </c>
+      <c r="B197" t="s">
+        <v>926</v>
+      </c>
+      <c r="C197" t="s">
+        <v>582</v>
+      </c>
+      <c r="D197" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E197" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F197" t="s">
+        <v>29</v>
+      </c>
+      <c r="G197" t="s">
+        <v>22</v>
+      </c>
+      <c r="H197" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>874</v>
+      </c>
+      <c r="B198" t="s">
+        <v>927</v>
+      </c>
+      <c r="C198" t="s">
+        <v>61</v>
+      </c>
+      <c r="D198" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E198" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F198" t="s">
+        <v>29</v>
+      </c>
+      <c r="G198" t="s">
+        <v>52</v>
+      </c>
+      <c r="H198" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>875</v>
+      </c>
+      <c r="B199" t="s">
+        <v>928</v>
+      </c>
+      <c r="C199" t="s">
+        <v>976</v>
+      </c>
+      <c r="D199" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E199" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F199" t="s">
+        <v>29</v>
+      </c>
+      <c r="G199" t="s">
+        <v>52</v>
+      </c>
+      <c r="H199" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>876</v>
+      </c>
+      <c r="B200" t="s">
+        <v>929</v>
+      </c>
+      <c r="C200" t="s">
+        <v>977</v>
+      </c>
+      <c r="D200" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E200" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F200" t="s">
+        <v>29</v>
+      </c>
+      <c r="G200" t="s">
+        <v>22</v>
+      </c>
+      <c r="H200" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>877</v>
+      </c>
+      <c r="B201" t="s">
+        <v>930</v>
+      </c>
+      <c r="C201" t="s">
+        <v>978</v>
+      </c>
+      <c r="D201" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E201" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F201" t="s">
+        <v>13</v>
+      </c>
+      <c r="G201" t="s">
+        <v>30</v>
+      </c>
+      <c r="H201" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>878</v>
+      </c>
+      <c r="B202" t="s">
+        <v>931</v>
+      </c>
+      <c r="C202" t="s">
+        <v>18</v>
+      </c>
+      <c r="D202" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E202" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F202" t="s">
+        <v>29</v>
+      </c>
+      <c r="G202" t="s">
+        <v>14</v>
+      </c>
+      <c r="H202" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>879</v>
+      </c>
+      <c r="B203" t="s">
+        <v>932</v>
+      </c>
+      <c r="C203" t="s">
+        <v>979</v>
+      </c>
+      <c r="D203" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E203" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F203" t="s">
+        <v>21</v>
+      </c>
+      <c r="G203" t="s">
+        <v>30</v>
+      </c>
+      <c r="H203" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>880</v>
+      </c>
+      <c r="B204" t="s">
+        <v>933</v>
+      </c>
+      <c r="C204" t="s">
+        <v>980</v>
+      </c>
+      <c r="D204" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E204" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F204" t="s">
+        <v>21</v>
+      </c>
+      <c r="G204" t="s">
+        <v>22</v>
+      </c>
+      <c r="H204" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>881</v>
+      </c>
+      <c r="B205" t="s">
+        <v>934</v>
+      </c>
+      <c r="C205" t="s">
+        <v>209</v>
+      </c>
+      <c r="D205" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E205" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F205" t="s">
+        <v>21</v>
+      </c>
+      <c r="G205" t="s">
+        <v>65</v>
+      </c>
+      <c r="H205" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>882</v>
+      </c>
+      <c r="B206" t="s">
+        <v>935</v>
+      </c>
+      <c r="C206" t="s">
+        <v>981</v>
+      </c>
+      <c r="D206" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E206" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F206" t="s">
+        <v>21</v>
+      </c>
+      <c r="G206" t="s">
+        <v>52</v>
+      </c>
+      <c r="H206" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>883</v>
+      </c>
+      <c r="B207" t="s">
+        <v>936</v>
+      </c>
+      <c r="C207" t="s">
+        <v>774</v>
+      </c>
+      <c r="D207" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E207" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F207" t="s">
+        <v>29</v>
+      </c>
+      <c r="G207" t="s">
+        <v>22</v>
+      </c>
+      <c r="H207" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>884</v>
+      </c>
+      <c r="B208" t="s">
+        <v>937</v>
+      </c>
+      <c r="C208" t="s">
+        <v>246</v>
+      </c>
+      <c r="D208" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E208" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G208" t="s">
+        <v>52</v>
+      </c>
+      <c r="H208" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>885</v>
+      </c>
+      <c r="B209" t="s">
+        <v>938</v>
+      </c>
+      <c r="C209" t="s">
+        <v>246</v>
+      </c>
+      <c r="D209" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E209" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F209" t="s">
+        <v>21</v>
+      </c>
+      <c r="G209" t="s">
+        <v>52</v>
+      </c>
+      <c r="H209" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>886</v>
+      </c>
+      <c r="B210" t="s">
+        <v>939</v>
+      </c>
+      <c r="C210" t="s">
+        <v>982</v>
+      </c>
+      <c r="D210" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E210" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F210" t="s">
+        <v>29</v>
+      </c>
+      <c r="G210" t="s">
+        <v>22</v>
+      </c>
+      <c r="H210" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>887</v>
+      </c>
+      <c r="B211" t="s">
+        <v>940</v>
+      </c>
+      <c r="C211" t="s">
+        <v>566</v>
+      </c>
+      <c r="D211" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E211" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F211" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G211" t="s">
+        <v>30</v>
+      </c>
+      <c r="H211" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>888</v>
+      </c>
+      <c r="B212" t="s">
+        <v>941</v>
+      </c>
+      <c r="C212" t="s">
+        <v>983</v>
+      </c>
+      <c r="D212" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E212" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F212" t="s">
+        <v>21</v>
+      </c>
+      <c r="G212" t="s">
+        <v>14</v>
+      </c>
+      <c r="H212" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>889</v>
+      </c>
+      <c r="B213" t="s">
+        <v>942</v>
+      </c>
+      <c r="C213" t="s">
+        <v>984</v>
+      </c>
+      <c r="D213" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E213" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F213" t="s">
+        <v>21</v>
+      </c>
+      <c r="G213" t="s">
+        <v>30</v>
+      </c>
+      <c r="H213" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>890</v>
+      </c>
+      <c r="B214" t="s">
+        <v>943</v>
+      </c>
+      <c r="C214" t="s">
+        <v>143</v>
+      </c>
+      <c r="D214" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E214" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F214" t="s">
+        <v>13</v>
+      </c>
+      <c r="G214" t="s">
+        <v>22</v>
+      </c>
+      <c r="H214" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>891</v>
+      </c>
+      <c r="B215" t="s">
+        <v>944</v>
+      </c>
+      <c r="C215" t="s">
+        <v>985</v>
+      </c>
+      <c r="D215" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E215" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F215" t="s">
+        <v>13</v>
+      </c>
+      <c r="G215" t="s">
+        <v>65</v>
+      </c>
+      <c r="H215" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>892</v>
+      </c>
+      <c r="B216" t="s">
+        <v>945</v>
+      </c>
+      <c r="C216" t="s">
+        <v>986</v>
+      </c>
+      <c r="D216" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E216" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F216" t="s">
+        <v>29</v>
+      </c>
+      <c r="G216" t="s">
+        <v>52</v>
+      </c>
+      <c r="H216" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>893</v>
+      </c>
+      <c r="B217" t="s">
+        <v>946</v>
+      </c>
+      <c r="C217" t="s">
+        <v>979</v>
+      </c>
+      <c r="D217" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E217" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F217" t="s">
+        <v>13</v>
+      </c>
+      <c r="G217" t="s">
+        <v>22</v>
+      </c>
+      <c r="H217" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>894</v>
+      </c>
+      <c r="B218" t="s">
+        <v>947</v>
+      </c>
+      <c r="C218" t="s">
+        <v>577</v>
+      </c>
+      <c r="D218" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E218" t="s">
+        <v>850</v>
+      </c>
+      <c r="F218" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G218" t="s">
+        <v>52</v>
+      </c>
+      <c r="H218" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>895</v>
+      </c>
+      <c r="B219" t="s">
+        <v>948</v>
+      </c>
+      <c r="C219" t="s">
+        <v>977</v>
+      </c>
+      <c r="D219" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E219" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F219" t="s">
+        <v>29</v>
+      </c>
+      <c r="G219" t="s">
+        <v>52</v>
+      </c>
+      <c r="H219" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>896</v>
+      </c>
+      <c r="B220" t="s">
+        <v>949</v>
+      </c>
+      <c r="C220" t="s">
+        <v>984</v>
+      </c>
+      <c r="D220" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E220" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F220" t="s">
+        <v>21</v>
+      </c>
+      <c r="G220" t="s">
+        <v>22</v>
+      </c>
+      <c r="H220" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>897</v>
+      </c>
+      <c r="B221" t="s">
+        <v>950</v>
+      </c>
+      <c r="C221" t="s">
+        <v>987</v>
+      </c>
+      <c r="D221" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E221" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F221" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G221" t="s">
+        <v>30</v>
+      </c>
+      <c r="H221" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>898</v>
+      </c>
+      <c r="B222" t="s">
+        <v>951</v>
+      </c>
+      <c r="C222" t="s">
+        <v>979</v>
+      </c>
+      <c r="D222" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E222" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F222" t="s">
+        <v>21</v>
+      </c>
+      <c r="G222" t="s">
+        <v>14</v>
+      </c>
+      <c r="H222" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>899</v>
+      </c>
+      <c r="B223" t="s">
+        <v>952</v>
+      </c>
+      <c r="C223" t="s">
+        <v>988</v>
+      </c>
+      <c r="D223" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E223" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F223" t="s">
+        <v>29</v>
+      </c>
+      <c r="G223" t="s">
+        <v>30</v>
+      </c>
+      <c r="H223" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>900</v>
+      </c>
+      <c r="B224" t="s">
+        <v>953</v>
+      </c>
+      <c r="C224" t="s">
+        <v>255</v>
+      </c>
+      <c r="D224" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E224" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F224" t="s">
+        <v>29</v>
+      </c>
+      <c r="G224" t="s">
+        <v>22</v>
+      </c>
+      <c r="H224" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>901</v>
+      </c>
+      <c r="B225" t="s">
+        <v>954</v>
+      </c>
+      <c r="C225" t="s">
+        <v>397</v>
+      </c>
+      <c r="D225" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E225" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F225" t="s">
+        <v>13</v>
+      </c>
+      <c r="G225" t="s">
+        <v>65</v>
+      </c>
+      <c r="H225" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>902</v>
+      </c>
+      <c r="B226" t="s">
+        <v>955</v>
+      </c>
+      <c r="C226" t="s">
+        <v>989</v>
+      </c>
+      <c r="D226" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E226" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F226" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G226" t="s">
+        <v>52</v>
+      </c>
+      <c r="H226" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>903</v>
+      </c>
+      <c r="B227" t="s">
+        <v>956</v>
+      </c>
+      <c r="C227" t="s">
+        <v>55</v>
+      </c>
+      <c r="D227" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E227" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F227" t="s">
+        <v>21</v>
+      </c>
+      <c r="G227" t="s">
+        <v>22</v>
+      </c>
+      <c r="H227" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>904</v>
+      </c>
+      <c r="B228" t="s">
+        <v>957</v>
+      </c>
+      <c r="C228" t="s">
+        <v>990</v>
+      </c>
+      <c r="D228" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E228" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F228" t="s">
+        <v>29</v>
+      </c>
+      <c r="G228" t="s">
+        <v>52</v>
+      </c>
+      <c r="H228" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>905</v>
+      </c>
+      <c r="B229" t="s">
+        <v>958</v>
+      </c>
+      <c r="C229" t="s">
+        <v>990</v>
+      </c>
+      <c r="D229" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E229" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F229" t="s">
+        <v>29</v>
+      </c>
+      <c r="G229" t="s">
+        <v>52</v>
+      </c>
+      <c r="H229" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>906</v>
+      </c>
+      <c r="B230" t="s">
+        <v>959</v>
+      </c>
+      <c r="C230" t="s">
+        <v>255</v>
+      </c>
+      <c r="D230" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E230" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F230" t="s">
+        <v>29</v>
+      </c>
+      <c r="G230" t="s">
+        <v>22</v>
+      </c>
+      <c r="H230" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>907</v>
+      </c>
+      <c r="B231" t="s">
+        <v>960</v>
+      </c>
+      <c r="C231" t="s">
+        <v>236</v>
+      </c>
+      <c r="D231" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E231" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F231" t="s">
+        <v>29</v>
+      </c>
+      <c r="G231" t="s">
+        <v>30</v>
+      </c>
+      <c r="H231" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>908</v>
+      </c>
+      <c r="B232" t="s">
+        <v>961</v>
+      </c>
+      <c r="C232" t="s">
+        <v>467</v>
+      </c>
+      <c r="D232" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E232" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F232" t="s">
+        <v>21</v>
+      </c>
+      <c r="G232" t="s">
+        <v>14</v>
+      </c>
+      <c r="H232" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>909</v>
+      </c>
+      <c r="B233" t="s">
+        <v>962</v>
+      </c>
+      <c r="C233" t="s">
+        <v>255</v>
+      </c>
+      <c r="D233" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E233" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F233" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G233" t="s">
+        <v>30</v>
+      </c>
+      <c r="H233" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>910</v>
+      </c>
+      <c r="B234" t="s">
+        <v>963</v>
+      </c>
+      <c r="C234" t="s">
+        <v>61</v>
+      </c>
+      <c r="D234" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E234" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F234" t="s">
+        <v>29</v>
+      </c>
+      <c r="G234" t="s">
+        <v>22</v>
+      </c>
+      <c r="H234" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>911</v>
+      </c>
+      <c r="B235" t="s">
+        <v>964</v>
+      </c>
+      <c r="C235" t="s">
+        <v>991</v>
+      </c>
+      <c r="D235" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E235" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F235" t="s">
+        <v>13</v>
+      </c>
+      <c r="G235" t="s">
+        <v>65</v>
+      </c>
+      <c r="H235" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>912</v>
+      </c>
+      <c r="B236" t="s">
+        <v>965</v>
+      </c>
+      <c r="C236" t="s">
+        <v>231</v>
+      </c>
+      <c r="D236" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E236" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F236" t="s">
+        <v>29</v>
+      </c>
+      <c r="G236" t="s">
+        <v>52</v>
+      </c>
+      <c r="H236" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>913</v>
+      </c>
+      <c r="B237" t="s">
+        <v>966</v>
+      </c>
+      <c r="C237" t="s">
+        <v>61</v>
+      </c>
+      <c r="D237" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E237" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F237" t="s">
+        <v>13</v>
+      </c>
+      <c r="G237" t="s">
+        <v>22</v>
+      </c>
+      <c r="H237" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>914</v>
+      </c>
+      <c r="B238" t="s">
+        <v>967</v>
+      </c>
+      <c r="C238" t="s">
+        <v>973</v>
+      </c>
+      <c r="D238" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E238" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F238" t="s">
+        <v>21</v>
+      </c>
+      <c r="G238" t="s">
+        <v>52</v>
+      </c>
+      <c r="H238" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>915</v>
+      </c>
+      <c r="B239" t="s">
+        <v>968</v>
+      </c>
+      <c r="C239" t="s">
+        <v>776</v>
+      </c>
+      <c r="D239" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E239" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F239" t="s">
+        <v>13</v>
+      </c>
+      <c r="G239" t="s">
+        <v>22</v>
+      </c>
+      <c r="H239" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>916</v>
+      </c>
+      <c r="B240" t="s">
+        <v>969</v>
+      </c>
+      <c r="C240" t="s">
+        <v>992</v>
+      </c>
+      <c r="D240" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F240" t="s">
+        <v>29</v>
+      </c>
+      <c r="G240" t="s">
+        <v>65</v>
+      </c>
+      <c r="H240" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>917</v>
+      </c>
+      <c r="B241" t="s">
+        <v>970</v>
+      </c>
+      <c r="C241" t="s">
+        <v>632</v>
+      </c>
+      <c r="D241" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E241" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F241" t="s">
+        <v>29</v>
+      </c>
+      <c r="G241" t="s">
+        <v>22</v>
+      </c>
+      <c r="H241" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>918</v>
+      </c>
+      <c r="B242" t="s">
+        <v>971</v>
+      </c>
+      <c r="C242" t="s">
+        <v>382</v>
+      </c>
+      <c r="D242" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E242" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F242" t="s">
+        <v>29</v>
+      </c>
+      <c r="G242" t="s">
+        <v>65</v>
+      </c>
+      <c r="H242" t="s">
+        <v>97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/public/Data.xlsx
+++ b/public/Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Website-Project\IKS\iks-digital-repository\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{191D07A5-1D69-4051-A2EB-E508243C4AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7A57FE0-760B-4511-BE49-A970F9AB74B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1930" uniqueCount="1114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2360" uniqueCount="1217">
   <si>
     <t>Voucher No</t>
   </si>
@@ -3390,9 +3390,6 @@
     <t>Narakoli</t>
   </si>
   <si>
-    <t xml:space="preserve"> Gajar ghas </t>
-  </si>
-  <si>
     <t>Climbing vine</t>
   </si>
   <si>
@@ -3445,6 +3442,318 @@
   </si>
   <si>
     <t>Leaf, stem, flower</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/110</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/111</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/112</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/113</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/114</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/115</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/116</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/117</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/118</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/119</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/120</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/121</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/122</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/123</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/124</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/125</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/126</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/127</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/128</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/129</t>
+  </si>
+  <si>
+    <t>IKS/Trident/K/130</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Tecoma stans</t>
+  </si>
+  <si>
+    <t>Sida rhombifolia</t>
+  </si>
+  <si>
+    <t>Catharanthus roseus</t>
+  </si>
+  <si>
+    <t>Synedrella nodiflora</t>
+  </si>
+  <si>
+    <t>Rosa indica</t>
+  </si>
+  <si>
+    <t>Boerhavia diffusa</t>
+  </si>
+  <si>
+    <t>Phyllanthus fraternus</t>
+  </si>
+  <si>
+    <t>Evolvulus alsinoides</t>
+  </si>
+  <si>
+    <t>Mucuna pruriens</t>
+  </si>
+  <si>
+    <t>Albizia lebbeck</t>
+  </si>
+  <si>
+    <t>Moringa oleifera</t>
+  </si>
+  <si>
+    <t>Morinda citrifolia</t>
+  </si>
+  <si>
+    <t>Caesalpinia sappan</t>
+  </si>
+  <si>
+    <t>Garcinia indica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holarrhena antidysenterica </t>
+  </si>
+  <si>
+    <t>Murraya koenigii</t>
+  </si>
+  <si>
+    <t>Artocarpus lacucha</t>
+  </si>
+  <si>
+    <t>Costus speciosus</t>
+  </si>
+  <si>
+    <t>Aegle marmelos (L.) Corr.</t>
+  </si>
+  <si>
+    <t>Rauwolfia serpentine (L.) Benth.ex. Kurz</t>
+  </si>
+  <si>
+    <t>Zingiber officinale Rosc.</t>
+  </si>
+  <si>
+    <t>Morinda tinctoria Roxb.</t>
+  </si>
+  <si>
+    <t>Operculina turpethum (Linn) Silva Manso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleomaceae </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosaceae </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nyctaginaceae </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabaceae </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moringaceae </t>
+  </si>
+  <si>
+    <t>Clusiaceae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rutaceae </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costaceae </t>
+  </si>
+  <si>
+    <t>It is used to treat diabetes, digestion issues, stomach pain, colds, fevers, and headaches. It is also used as antidote for insect, rat, or snake bites.</t>
+  </si>
+  <si>
+    <t>It is used for treating inflammation, rheumatism, and digestive disorders</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It is used as anti-cancer agent, to help manage diabetes, treat blood dysentery, wounds </t>
+  </si>
+  <si>
+    <t>It is used for treatment of wound, Pain and Inflammation and also some Neurological Conditions</t>
+  </si>
+  <si>
+    <t>It is edible and used in folk medicine to ease pain, reduce fevers, and treat early malaria symptoms</t>
+  </si>
+  <si>
+    <t>It is used as ornamental and used for mild laxative, antioxidant, antibacterial, and anti-inflammatory benefits</t>
+  </si>
+  <si>
+    <t>It is used to treat Kidney and Bladder Stones, diabetes. It is used as stones.Diuretic and Anti-Inflammatory agent</t>
+  </si>
+  <si>
+    <t>It is used for wound healing, anti-inflammatory relief, and infection management</t>
+  </si>
+  <si>
+    <t>It is used for liver Protection, Diuretic and Kidney Health: Anti-Inflammatory and Pain Relief.</t>
+  </si>
+  <si>
+    <t>It is used to treat liver disorders, kidney stones, and urinary infections</t>
+  </si>
+  <si>
+    <t>It is used as a brain tonic, memory enhancer, and fever reducer</t>
+  </si>
+  <si>
+    <t>It is used in herbal practices to help manage stress, anxiety, and as a natural tonic to support sexual health.It is also used to treat pain, inflammation, and blood sugar management</t>
+  </si>
+  <si>
+    <t>It is used for treating respiratory conditions, allergies, skin disorders, inflammation, insomnia.</t>
+  </si>
+  <si>
+    <t>It is used in folk medicine for managing inflammation, blood sugar levels, and digestive health</t>
+  </si>
+  <si>
+    <t>It has been used to treat the common cold, bacterial infections, fevers, and gastrointestinal problems.</t>
+  </si>
+  <si>
+    <t>It has anti-inflammatory, antimicrobial, and blood-purifying properties</t>
+  </si>
+  <si>
+    <t>It is used to treat digestive problems, skin damage, and body inflammation</t>
+  </si>
+  <si>
+    <t>It is used to treat amoebic dysentery, diarrhea, skin ailments, diabetes, and inflammatory conditions</t>
+  </si>
+  <si>
+    <t>It is used in treating piles, inflammation, itching, fresh cuts, dysentery, bruises, and edema</t>
+  </si>
+  <si>
+    <t>It has anti-inflammatory, antiviral, anticancer and anti-HIV properties, anti-aging activity, antioxidant and anti-glycation properties</t>
+  </si>
+  <si>
+    <t>It has anti-inflammatory, antidiabetic, and antimicrobial properties</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gajar ghas </t>
+  </si>
+  <si>
+    <t>Halidia tipokamia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bajramuli </t>
+  </si>
+  <si>
+    <t>Sada Bihari</t>
+  </si>
+  <si>
+    <t>Golap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paunsia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pokasunga </t>
+  </si>
+  <si>
+    <t>Punarva</t>
+  </si>
+  <si>
+    <t>Bhuin Anla</t>
+  </si>
+  <si>
+    <t>Vishnukranti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baidanka </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sirisha </t>
+  </si>
+  <si>
+    <t>Sajana</t>
+  </si>
+  <si>
+    <t>Noni</t>
+  </si>
+  <si>
+    <t>Patranga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tintali </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kutaja </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bhursunga </t>
+  </si>
+  <si>
+    <t>Jeuto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kauberi </t>
+  </si>
+  <si>
+    <t>Perennial subshrub</t>
+  </si>
+  <si>
+    <t>Leaves, roots, flowers, bark, and seeds</t>
+  </si>
+  <si>
+    <t>Leaves, Root &amp; Seed</t>
+  </si>
+  <si>
+    <t>Leaves and Seed</t>
+  </si>
+  <si>
+    <t>Seeds and roots</t>
+  </si>
+  <si>
+    <t>Leaf, bark, flower and seed</t>
+  </si>
+  <si>
+    <t>Bark, root, seed</t>
+  </si>
+  <si>
+    <t>Fruit, seed</t>
+  </si>
+  <si>
+    <t>Leaf, seed, bark, flower</t>
+  </si>
+  <si>
+    <t>Leaf, seed, bark, fruit</t>
+  </si>
+  <si>
+    <t>Rhizome, leaves, and stems</t>
   </si>
 </sst>
 </file>
@@ -3850,7 +4159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H242"/>
+  <dimension ref="A1:H296"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.59765625" bestFit="1" customWidth="1"/>
@@ -8762,7 +9071,7 @@
         <v>52</v>
       </c>
       <c r="H189" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
@@ -8915,7 +9224,7 @@
         <v>65</v>
       </c>
       <c r="H195" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
@@ -8941,7 +9250,7 @@
         <v>52</v>
       </c>
       <c r="H196" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
@@ -9019,7 +9328,7 @@
         <v>52</v>
       </c>
       <c r="H199" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
@@ -9097,7 +9406,7 @@
         <v>14</v>
       </c>
       <c r="H202" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
@@ -9149,7 +9458,7 @@
         <v>22</v>
       </c>
       <c r="H204" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
@@ -9175,7 +9484,7 @@
         <v>65</v>
       </c>
       <c r="H205" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
@@ -9201,7 +9510,7 @@
         <v>52</v>
       </c>
       <c r="H206" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
@@ -9305,7 +9614,7 @@
         <v>22</v>
       </c>
       <c r="H210" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
@@ -9325,7 +9634,7 @@
         <v>1066</v>
       </c>
       <c r="F211" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G211" t="s">
         <v>30</v>
@@ -9357,7 +9666,7 @@
         <v>14</v>
       </c>
       <c r="H212" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
@@ -9383,7 +9692,7 @@
         <v>30</v>
       </c>
       <c r="H213" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
@@ -9435,7 +9744,7 @@
         <v>65</v>
       </c>
       <c r="H215" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
@@ -9487,7 +9796,7 @@
         <v>22</v>
       </c>
       <c r="H217" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
@@ -9507,7 +9816,7 @@
         <v>850</v>
       </c>
       <c r="F218" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G218" t="s">
         <v>52</v>
@@ -9565,7 +9874,7 @@
         <v>22</v>
       </c>
       <c r="H220" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
@@ -9585,7 +9894,7 @@
         <v>1075</v>
       </c>
       <c r="F221" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G221" t="s">
         <v>30</v>
@@ -9695,7 +10004,7 @@
         <v>65</v>
       </c>
       <c r="H225" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.3">
@@ -9715,7 +10024,7 @@
         <v>1080</v>
       </c>
       <c r="F226" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G226" t="s">
         <v>52</v>
@@ -9799,7 +10108,7 @@
         <v>52</v>
       </c>
       <c r="H229" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
@@ -9877,7 +10186,7 @@
         <v>14</v>
       </c>
       <c r="H232" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.3">
@@ -9897,7 +10206,7 @@
         <v>1087</v>
       </c>
       <c r="F233" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="G233" t="s">
         <v>30</v>
@@ -9955,7 +10264,7 @@
         <v>65</v>
       </c>
       <c r="H235" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.3">
@@ -10082,7 +10391,7 @@
         <v>65</v>
       </c>
       <c r="H240" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.3">
@@ -10125,7 +10434,7 @@
         <v>1045</v>
       </c>
       <c r="E242" t="s">
-        <v>1095</v>
+        <v>1186</v>
       </c>
       <c r="F242" t="s">
         <v>29</v>
@@ -10135,6 +10444,1404 @@
       </c>
       <c r="H242" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A243" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="B243" t="s">
+        <v>740</v>
+      </c>
+      <c r="C243" t="s">
+        <v>772</v>
+      </c>
+      <c r="D243" t="s">
+        <v>786</v>
+      </c>
+      <c r="E243" t="s">
+        <v>820</v>
+      </c>
+      <c r="F243" t="s">
+        <v>29</v>
+      </c>
+      <c r="G243" t="s">
+        <v>400</v>
+      </c>
+      <c r="H243" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>708</v>
+      </c>
+      <c r="B244" t="s">
+        <v>741</v>
+      </c>
+      <c r="C244" t="s">
+        <v>773</v>
+      </c>
+      <c r="D244" t="s">
+        <v>787</v>
+      </c>
+      <c r="E244" t="s">
+        <v>821</v>
+      </c>
+      <c r="F244" t="s">
+        <v>29</v>
+      </c>
+      <c r="G244" t="s">
+        <v>411</v>
+      </c>
+      <c r="H244" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>709</v>
+      </c>
+      <c r="B245" t="s">
+        <v>742</v>
+      </c>
+      <c r="C245" t="s">
+        <v>403</v>
+      </c>
+      <c r="D245" t="s">
+        <v>788</v>
+      </c>
+      <c r="E245" t="s">
+        <v>822</v>
+      </c>
+      <c r="F245" t="s">
+        <v>29</v>
+      </c>
+      <c r="G245" t="s">
+        <v>406</v>
+      </c>
+      <c r="H245" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>710</v>
+      </c>
+      <c r="B246" t="s">
+        <v>743</v>
+      </c>
+      <c r="C246" t="s">
+        <v>774</v>
+      </c>
+      <c r="D246" t="s">
+        <v>789</v>
+      </c>
+      <c r="E246" t="s">
+        <v>823</v>
+      </c>
+      <c r="F246" t="s">
+        <v>13</v>
+      </c>
+      <c r="G246" t="s">
+        <v>411</v>
+      </c>
+      <c r="H246" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>711</v>
+      </c>
+      <c r="B247" t="s">
+        <v>744</v>
+      </c>
+      <c r="C247" t="s">
+        <v>775</v>
+      </c>
+      <c r="D247" t="s">
+        <v>790</v>
+      </c>
+      <c r="E247" t="s">
+        <v>824</v>
+      </c>
+      <c r="F247" t="s">
+        <v>29</v>
+      </c>
+      <c r="G247" t="s">
+        <v>400</v>
+      </c>
+      <c r="H247" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>712</v>
+      </c>
+      <c r="B248" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C248" t="s">
+        <v>776</v>
+      </c>
+      <c r="D248" t="s">
+        <v>791</v>
+      </c>
+      <c r="E248" t="s">
+        <v>825</v>
+      </c>
+      <c r="F248" t="s">
+        <v>21</v>
+      </c>
+      <c r="G248" t="s">
+        <v>406</v>
+      </c>
+      <c r="H248" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>713</v>
+      </c>
+      <c r="B249" t="s">
+        <v>746</v>
+      </c>
+      <c r="C249" t="s">
+        <v>83</v>
+      </c>
+      <c r="D249" t="s">
+        <v>792</v>
+      </c>
+      <c r="E249" t="s">
+        <v>826</v>
+      </c>
+      <c r="F249" t="s">
+        <v>21</v>
+      </c>
+      <c r="G249" t="s">
+        <v>411</v>
+      </c>
+      <c r="H249" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>714</v>
+      </c>
+      <c r="B250" t="s">
+        <v>747</v>
+      </c>
+      <c r="C250" t="s">
+        <v>777</v>
+      </c>
+      <c r="D250" t="s">
+        <v>793</v>
+      </c>
+      <c r="E250" t="s">
+        <v>827</v>
+      </c>
+      <c r="F250" t="s">
+        <v>29</v>
+      </c>
+      <c r="G250" t="s">
+        <v>406</v>
+      </c>
+      <c r="H250" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>715</v>
+      </c>
+      <c r="B251" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C251" t="s">
+        <v>778</v>
+      </c>
+      <c r="D251" t="s">
+        <v>794</v>
+      </c>
+      <c r="E251" t="s">
+        <v>828</v>
+      </c>
+      <c r="F251" t="s">
+        <v>13</v>
+      </c>
+      <c r="G251" t="s">
+        <v>406</v>
+      </c>
+      <c r="H251" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>716</v>
+      </c>
+      <c r="B252" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C252" t="s">
+        <v>161</v>
+      </c>
+      <c r="D252" t="s">
+        <v>795</v>
+      </c>
+      <c r="E252" t="s">
+        <v>829</v>
+      </c>
+      <c r="F252" t="s">
+        <v>29</v>
+      </c>
+      <c r="G252" t="s">
+        <v>455</v>
+      </c>
+      <c r="H252" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>717</v>
+      </c>
+      <c r="B253" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C253" t="s">
+        <v>236</v>
+      </c>
+      <c r="D253" t="s">
+        <v>796</v>
+      </c>
+      <c r="E253" t="s">
+        <v>830</v>
+      </c>
+      <c r="F253" t="s">
+        <v>21</v>
+      </c>
+      <c r="G253" t="s">
+        <v>400</v>
+      </c>
+      <c r="H253" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>718</v>
+      </c>
+      <c r="B254" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C254" t="s">
+        <v>779</v>
+      </c>
+      <c r="D254" t="s">
+        <v>797</v>
+      </c>
+      <c r="E254" t="s">
+        <v>831</v>
+      </c>
+      <c r="F254" t="s">
+        <v>29</v>
+      </c>
+      <c r="G254" t="s">
+        <v>406</v>
+      </c>
+      <c r="H254" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>719</v>
+      </c>
+      <c r="B255" t="s">
+        <v>752</v>
+      </c>
+      <c r="C255" t="s">
+        <v>545</v>
+      </c>
+      <c r="D255" t="s">
+        <v>798</v>
+      </c>
+      <c r="E255" t="s">
+        <v>832</v>
+      </c>
+      <c r="F255" t="s">
+        <v>29</v>
+      </c>
+      <c r="G255" t="s">
+        <v>411</v>
+      </c>
+      <c r="H255" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>720</v>
+      </c>
+      <c r="B256" t="s">
+        <v>753</v>
+      </c>
+      <c r="C256" t="s">
+        <v>428</v>
+      </c>
+      <c r="D256" t="s">
+        <v>799</v>
+      </c>
+      <c r="E256" t="s">
+        <v>833</v>
+      </c>
+      <c r="F256" t="s">
+        <v>29</v>
+      </c>
+      <c r="G256" t="s">
+        <v>455</v>
+      </c>
+      <c r="H256" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>721</v>
+      </c>
+      <c r="B257" t="s">
+        <v>754</v>
+      </c>
+      <c r="C257" t="s">
+        <v>687</v>
+      </c>
+      <c r="D257" t="s">
+        <v>800</v>
+      </c>
+      <c r="E257" t="s">
+        <v>834</v>
+      </c>
+      <c r="F257" t="s">
+        <v>29</v>
+      </c>
+      <c r="G257" t="s">
+        <v>400</v>
+      </c>
+      <c r="H257" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>722</v>
+      </c>
+      <c r="B258" t="s">
+        <v>755</v>
+      </c>
+      <c r="C258" t="s">
+        <v>780</v>
+      </c>
+      <c r="D258" t="s">
+        <v>801</v>
+      </c>
+      <c r="E258" t="s">
+        <v>835</v>
+      </c>
+      <c r="F258" t="s">
+        <v>29</v>
+      </c>
+      <c r="G258" t="s">
+        <v>406</v>
+      </c>
+      <c r="H258" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>723</v>
+      </c>
+      <c r="B259" t="s">
+        <v>756</v>
+      </c>
+      <c r="C259" t="s">
+        <v>18</v>
+      </c>
+      <c r="D259" t="s">
+        <v>802</v>
+      </c>
+      <c r="E259" t="s">
+        <v>836</v>
+      </c>
+      <c r="F259" t="s">
+        <v>13</v>
+      </c>
+      <c r="G259" t="s">
+        <v>411</v>
+      </c>
+      <c r="H259" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>724</v>
+      </c>
+      <c r="B260" t="s">
+        <v>757</v>
+      </c>
+      <c r="C260" t="s">
+        <v>77</v>
+      </c>
+      <c r="D260" t="s">
+        <v>803</v>
+      </c>
+      <c r="E260" t="s">
+        <v>837</v>
+      </c>
+      <c r="F260" t="s">
+        <v>21</v>
+      </c>
+      <c r="G260" t="s">
+        <v>406</v>
+      </c>
+      <c r="H260" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>725</v>
+      </c>
+      <c r="B261" t="s">
+        <v>758</v>
+      </c>
+      <c r="C261" t="s">
+        <v>781</v>
+      </c>
+      <c r="D261" t="s">
+        <v>804</v>
+      </c>
+      <c r="E261" t="s">
+        <v>838</v>
+      </c>
+      <c r="F261" t="s">
+        <v>29</v>
+      </c>
+      <c r="G261" t="s">
+        <v>455</v>
+      </c>
+      <c r="H261" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>726</v>
+      </c>
+      <c r="B262" t="s">
+        <v>759</v>
+      </c>
+      <c r="C262" t="s">
+        <v>255</v>
+      </c>
+      <c r="D262" t="s">
+        <v>805</v>
+      </c>
+      <c r="E262" t="s">
+        <v>839</v>
+      </c>
+      <c r="F262" t="s">
+        <v>13</v>
+      </c>
+      <c r="G262" t="s">
+        <v>455</v>
+      </c>
+      <c r="H262" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>727</v>
+      </c>
+      <c r="B263" t="s">
+        <v>760</v>
+      </c>
+      <c r="C263" t="s">
+        <v>161</v>
+      </c>
+      <c r="D263" t="s">
+        <v>806</v>
+      </c>
+      <c r="E263" t="s">
+        <v>840</v>
+      </c>
+      <c r="F263" t="s">
+        <v>29</v>
+      </c>
+      <c r="G263" t="s">
+        <v>411</v>
+      </c>
+      <c r="H263" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>728</v>
+      </c>
+      <c r="B264" t="s">
+        <v>761</v>
+      </c>
+      <c r="C264" t="s">
+        <v>782</v>
+      </c>
+      <c r="D264" t="s">
+        <v>807</v>
+      </c>
+      <c r="E264" t="s">
+        <v>841</v>
+      </c>
+      <c r="F264" t="s">
+        <v>569</v>
+      </c>
+      <c r="G264" t="s">
+        <v>406</v>
+      </c>
+      <c r="H264" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>729</v>
+      </c>
+      <c r="B265" t="s">
+        <v>762</v>
+      </c>
+      <c r="C265" t="s">
+        <v>44</v>
+      </c>
+      <c r="D265" t="s">
+        <v>808</v>
+      </c>
+      <c r="E265" t="s">
+        <v>842</v>
+      </c>
+      <c r="F265" t="s">
+        <v>569</v>
+      </c>
+      <c r="G265" t="s">
+        <v>406</v>
+      </c>
+      <c r="H265" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>730</v>
+      </c>
+      <c r="B266" t="s">
+        <v>763</v>
+      </c>
+      <c r="C266" t="s">
+        <v>687</v>
+      </c>
+      <c r="D266" t="s">
+        <v>809</v>
+      </c>
+      <c r="E266" t="s">
+        <v>843</v>
+      </c>
+      <c r="F266" t="s">
+        <v>29</v>
+      </c>
+      <c r="G266" t="s">
+        <v>455</v>
+      </c>
+      <c r="H266" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>731</v>
+      </c>
+      <c r="B267" t="s">
+        <v>764</v>
+      </c>
+      <c r="C267" t="s">
+        <v>783</v>
+      </c>
+      <c r="D267" t="s">
+        <v>810</v>
+      </c>
+      <c r="E267" t="s">
+        <v>844</v>
+      </c>
+      <c r="F267" t="s">
+        <v>569</v>
+      </c>
+      <c r="G267" t="s">
+        <v>400</v>
+      </c>
+      <c r="H267" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>732</v>
+      </c>
+      <c r="B268" t="s">
+        <v>765</v>
+      </c>
+      <c r="C268" t="s">
+        <v>403</v>
+      </c>
+      <c r="D268" t="s">
+        <v>811</v>
+      </c>
+      <c r="E268" t="s">
+        <v>845</v>
+      </c>
+      <c r="F268" t="s">
+        <v>29</v>
+      </c>
+      <c r="G268" t="s">
+        <v>406</v>
+      </c>
+      <c r="H268" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>733</v>
+      </c>
+      <c r="B269" t="s">
+        <v>766</v>
+      </c>
+      <c r="C269" t="s">
+        <v>77</v>
+      </c>
+      <c r="D269" t="s">
+        <v>812</v>
+      </c>
+      <c r="E269" t="s">
+        <v>846</v>
+      </c>
+      <c r="F269" t="s">
+        <v>29</v>
+      </c>
+      <c r="G269" t="s">
+        <v>455</v>
+      </c>
+      <c r="H269" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>734</v>
+      </c>
+      <c r="B270" t="s">
+        <v>767</v>
+      </c>
+      <c r="C270" t="s">
+        <v>77</v>
+      </c>
+      <c r="D270" t="s">
+        <v>813</v>
+      </c>
+      <c r="E270" t="s">
+        <v>847</v>
+      </c>
+      <c r="F270" t="s">
+        <v>29</v>
+      </c>
+      <c r="G270" t="s">
+        <v>400</v>
+      </c>
+      <c r="H270" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>735</v>
+      </c>
+      <c r="B271" t="s">
+        <v>768</v>
+      </c>
+      <c r="C271" t="s">
+        <v>18</v>
+      </c>
+      <c r="D271" t="s">
+        <v>814</v>
+      </c>
+      <c r="E271" t="s">
+        <v>848</v>
+      </c>
+      <c r="F271" t="s">
+        <v>29</v>
+      </c>
+      <c r="G271" t="s">
+        <v>411</v>
+      </c>
+      <c r="H271" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>736</v>
+      </c>
+      <c r="B272" t="s">
+        <v>769</v>
+      </c>
+      <c r="C272" t="s">
+        <v>255</v>
+      </c>
+      <c r="D272" t="s">
+        <v>815</v>
+      </c>
+      <c r="E272" t="s">
+        <v>624</v>
+      </c>
+      <c r="F272" t="s">
+        <v>29</v>
+      </c>
+      <c r="G272" t="s">
+        <v>400</v>
+      </c>
+      <c r="H272" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>737</v>
+      </c>
+      <c r="B273" t="s">
+        <v>113</v>
+      </c>
+      <c r="C273" t="s">
+        <v>403</v>
+      </c>
+      <c r="D273" t="s">
+        <v>816</v>
+      </c>
+      <c r="E273" t="s">
+        <v>849</v>
+      </c>
+      <c r="F273" t="s">
+        <v>29</v>
+      </c>
+      <c r="G273" t="s">
+        <v>406</v>
+      </c>
+      <c r="H273" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>738</v>
+      </c>
+      <c r="B274" t="s">
+        <v>770</v>
+      </c>
+      <c r="C274" t="s">
+        <v>577</v>
+      </c>
+      <c r="D274" t="s">
+        <v>817</v>
+      </c>
+      <c r="E274" t="s">
+        <v>850</v>
+      </c>
+      <c r="F274" t="s">
+        <v>29</v>
+      </c>
+      <c r="G274" t="s">
+        <v>455</v>
+      </c>
+      <c r="H274" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>739</v>
+      </c>
+      <c r="B275" t="s">
+        <v>771</v>
+      </c>
+      <c r="C275" t="s">
+        <v>784</v>
+      </c>
+      <c r="D275" t="s">
+        <v>818</v>
+      </c>
+      <c r="E275" t="s">
+        <v>851</v>
+      </c>
+      <c r="F275" t="s">
+        <v>29</v>
+      </c>
+      <c r="G275" t="s">
+        <v>400</v>
+      </c>
+      <c r="H275" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B276" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C276" t="s">
+        <v>204</v>
+      </c>
+      <c r="D276" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E276" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F276" t="s">
+        <v>13</v>
+      </c>
+      <c r="G276" t="s">
+        <v>411</v>
+      </c>
+      <c r="H276" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B277" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C277" t="s">
+        <v>77</v>
+      </c>
+      <c r="D277" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E277" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F277" t="s">
+        <v>1206</v>
+      </c>
+      <c r="G277" t="s">
+        <v>411</v>
+      </c>
+      <c r="H277" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B278" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C278" t="s">
+        <v>428</v>
+      </c>
+      <c r="D278" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E278" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F278" t="s">
+        <v>29</v>
+      </c>
+      <c r="G278" t="s">
+        <v>455</v>
+      </c>
+      <c r="H278" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B279" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C279" t="s">
+        <v>582</v>
+      </c>
+      <c r="D279" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F279" t="s">
+        <v>29</v>
+      </c>
+      <c r="G279" t="s">
+        <v>406</v>
+      </c>
+      <c r="H279" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B280" t="s">
+        <v>486</v>
+      </c>
+      <c r="C280" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D280" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E280" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F280" t="s">
+        <v>29</v>
+      </c>
+      <c r="G280" t="s">
+        <v>411</v>
+      </c>
+      <c r="H280" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B281" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C281" t="s">
+        <v>1158</v>
+      </c>
+      <c r="D281" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E281" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F281" t="s">
+        <v>13</v>
+      </c>
+      <c r="G281" t="s">
+        <v>455</v>
+      </c>
+      <c r="H281" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B282" t="s">
+        <v>402</v>
+      </c>
+      <c r="C282" t="s">
+        <v>26</v>
+      </c>
+      <c r="D282" t="s">
+        <v>1171</v>
+      </c>
+      <c r="E282" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F282" t="s">
+        <v>29</v>
+      </c>
+      <c r="G282" t="s">
+        <v>455</v>
+      </c>
+      <c r="H282" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B283" t="s">
+        <v>408</v>
+      </c>
+      <c r="C283" t="s">
+        <v>582</v>
+      </c>
+      <c r="D283" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E283" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F283" t="s">
+        <v>29</v>
+      </c>
+      <c r="G283" t="s">
+        <v>406</v>
+      </c>
+      <c r="H283" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B284" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C284" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D284" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E284" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F284" t="s">
+        <v>29</v>
+      </c>
+      <c r="G284" t="s">
+        <v>406</v>
+      </c>
+      <c r="H284" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B285" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C285" t="s">
+        <v>397</v>
+      </c>
+      <c r="D285" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E285" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F285" t="s">
+        <v>29</v>
+      </c>
+      <c r="G285" t="s">
+        <v>406</v>
+      </c>
+      <c r="H285" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B286" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C286" t="s">
+        <v>566</v>
+      </c>
+      <c r="D286" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E286" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F286" t="s">
+        <v>29</v>
+      </c>
+      <c r="G286" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B287" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C287" t="s">
+        <v>18</v>
+      </c>
+      <c r="D287" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E287" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F287" t="s">
+        <v>13</v>
+      </c>
+      <c r="G287" t="s">
+        <v>455</v>
+      </c>
+      <c r="H287" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B288" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C288" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D288" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E288" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F288" t="s">
+        <v>21</v>
+      </c>
+      <c r="G288" t="s">
+        <v>411</v>
+      </c>
+      <c r="H288" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B289" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C289" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D289" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E289" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F289" t="s">
+        <v>21</v>
+      </c>
+      <c r="G289" t="s">
+        <v>455</v>
+      </c>
+      <c r="H289" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B290" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C290" t="s">
+        <v>236</v>
+      </c>
+      <c r="D290" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E290" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F290" t="s">
+        <v>13</v>
+      </c>
+      <c r="G290" t="s">
+        <v>400</v>
+      </c>
+      <c r="H290" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B291" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C291" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D291" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E291" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F291" t="s">
+        <v>21</v>
+      </c>
+      <c r="G291" t="s">
+        <v>411</v>
+      </c>
+      <c r="H291" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B292" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C292" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D292" t="s">
+        <v>1181</v>
+      </c>
+      <c r="E292" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F292" t="s">
+        <v>21</v>
+      </c>
+      <c r="G292" t="s">
+        <v>400</v>
+      </c>
+      <c r="H292" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B293" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C293" t="s">
+        <v>428</v>
+      </c>
+      <c r="D293" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E293" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F293" t="s">
+        <v>13</v>
+      </c>
+      <c r="G293" t="s">
+        <v>400</v>
+      </c>
+      <c r="H293" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B294" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C294" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D294" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E294" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F294" t="s">
+        <v>21</v>
+      </c>
+      <c r="G294" t="s">
+        <v>455</v>
+      </c>
+      <c r="H294" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B295" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C295" t="s">
+        <v>209</v>
+      </c>
+      <c r="D295" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E295" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F295" t="s">
+        <v>21</v>
+      </c>
+      <c r="G295" t="s">
+        <v>406</v>
+      </c>
+      <c r="H295" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B296" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C296" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D296" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E296" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F296" t="s">
+        <v>29</v>
+      </c>
+      <c r="G296" t="s">
+        <v>455</v>
+      </c>
+      <c r="H296" t="s">
+        <v>1216</v>
       </c>
     </row>
   </sheetData>
